--- a/testcase_list.xlsx
+++ b/testcase_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,70 +441,75 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>用例类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>驱动类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>时长</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>带宽目标</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>包大小</t>
+          <t>必选/可选</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>协议</t>
+          <t>对应Python文件</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>并发流</t>
+          <t>测试目的</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>参数1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>参数2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>参数3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>参数4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>参数5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>流量工具</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>必选/可选</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>用例类型</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>对应Python文件</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>最后更新时间</t>
         </is>
@@ -523,64 +528,69 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>30min</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -599,64 +609,69 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="M3" t="n">
         <v>16</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -675,64 +690,69 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="M4" t="n">
         <v>16</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -751,64 +771,69 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>64B</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="M5" t="n">
         <v>32</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -827,64 +852,69 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>64KB</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="M6" t="n">
         <v>8</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -903,64 +933,69 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>9000B</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="M7" t="n">
         <v>8</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -979,64 +1014,69 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="M8" t="n">
         <v>16</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1055,64 +1095,69 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>24h</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>TCP</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="M9" t="n">
         <v>8</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>iperf3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1131,64 +1176,69 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>UDP</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="M10" t="n">
         <v>16</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>iperf3 -u</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1207,64 +1257,69 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>64B</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>UDP</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="M11" t="n">
         <v>32</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>iperf3 -u</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1283,64 +1338,69 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>kernel</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>64B</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>UDP</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="M12" t="n">
         <v>64</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>iperf3 -u</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1359,64 +1419,69 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>dpdk</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>16</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>pktgen</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1435,64 +1500,69 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>dpdk</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>64B</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>32</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>pktgen</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1511,64 +1581,69 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>dpdk</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>1500B</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
         <v>16</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>pktgen</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1587,64 +1662,69 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>rdma</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>ib_write_bw -b</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="M16" t="n">
         <v>256</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>perftest</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1663,64 +1743,69 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>rdma</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>ib_read_bw -b</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="M17" t="n">
         <v>256</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>perftest</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1739,64 +1824,69 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>rdma</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>ib_send_bw -b</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="M18" t="n">
         <v>256</v>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>perftest</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>必选</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
@@ -1815,64 +1905,2713 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>stress</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>rdma</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>testcase/stress_test.py</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>30min</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>ib_write_lat</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="M19" t="n">
         <v>256</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>perftest</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LT-001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kernel快速长时测试-24h</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>longevity</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>必选</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>testcase/stress_test.py</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>testcase/longevity_test.py</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>24h</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1500B</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>iperf3</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LT-002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kernel标准长时测试-7x24h</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>longevity</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>testcase/longevity_test.py</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>168h</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1500B</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>iperf3</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LT-003</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kernel深度长时测试-15天</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>longevity</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>testcase/longevity_test.py</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>360h</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1500B</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>8</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>iperf3</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LT-004</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DPDK标准长时测试-7x24h</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>longevity</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>testcase/longevity_test.py</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>168h</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1500B</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>pktgen</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LT-005</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RDMA标准长时测试-7x24h</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>longevity</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>rdma</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>testcase/longevity_test.py</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>168h</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>ib_write_bw</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>perftest</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LT-006</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kernel周期波动流量测试</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>longevity</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>testcase/longevity_test.py</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>168h</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>50%~90%波动</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1500B</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>8</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>iperf3</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AN-001</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kernel链路中断测试</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>链路中断</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ifconfig down/up</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>链路UP+流量恢复30s</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AN-002</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kernel驱动重启测试</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>驱动重启</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>modprobe -r/r driver</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>驱动可用+流量恢复30s</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AN-003</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kernel流量突发测试</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>流量突发</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>瞬时90%带宽高压</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>流量稳定</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AN-004</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kernel SYN Flood攻击</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DDoS攻击</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>hping3 -S flood</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>攻击结束流量恢复</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AN-005</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kernel UDP Flood攻击</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>DDoS攻击</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>hping3 -2 flood</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>攻击结束流量恢复</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AN-006</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kernel畸形包测试-超大包</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>畸形包</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>tcpreplay oversized packet</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>error记录</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AN-007</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kernel畸形包测试-超小包</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>畸形包</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>tcpreplay undersize packet</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>error记录</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AN-008</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kernel小包PPS攻击</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>小包攻击</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>iperf3 -u -l 64 -P 64</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>流量恢复</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AN-009</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kernel队列数和队列深度组合测试</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>队列配置变更</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ethtool修改队列数/深度组合</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>流量稳定+error计数</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AN-010</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DPDK链路中断测试</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>链路中断</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ifconfig down/up</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>DPDK重初始化+流量恢复</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AN-011</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DPDK驱动重启测试</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>驱动重启</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DPDK rebind/reinit</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>DPDK可用+流量恢复</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AN-012</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DPDK SYN Flood攻击</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>DDoS攻击</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>hping3 -S flood</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>应用层恢复</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AN-013</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DPDK小包PPS攻击</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>小包攻击</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>pktgen high PPS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>流量恢复</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AN-014</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RDMA异常恢复测试</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>anomaly</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>rdma</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>testcase/anomaly_test.py</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>RDMA异常</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>QP状态异常恢复</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>QP状态恢复</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MX-001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kernel包大小混合测试</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mixed_data</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>testcase/mixed_data_test.py</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>包大小混合</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>64B(20%)+512B(30%)+1500B(40%)+64KB(10%)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>iperf3多流</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MX-002</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kernel协议混合测试</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>mixed_data</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>testcase/mixed_data_test.py</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>协议混合</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>TCP(60%)+UDP(40%)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>iperf3 TCP+UDP</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MX-003</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kernel全混合测试</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>mixed_data</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>testcase/mixed_data_test.py</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>包大小+协议混合</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>包大小混合+协议混合</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>iperf3多流</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MX-004</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DPDK包大小混合测试</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>mixed_data</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>testcase/mixed_data_test.py</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>包大小混合</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>64B(20%)+512B(30%)+1500B(40%)+64KB(10%)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>pktgen</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MX-005</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DPDK协议混合测试</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mixed_data</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>testcase/mixed_data_test.py</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>协议混合</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>TCP(60%)+UDP(40%)模拟</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>pktgen</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MX-006</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>DPDK全混合测试</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mixed_data</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>dpdk</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>testcase/mixed_data_test.py</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>包大小+协议混合</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>包大小混合+协议混合</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>pktgen</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BF-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Web服务业务流测试</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>business_flow</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>testcase/business_flow_test.py</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Web服务</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>nginx</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ab/curl</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BF-002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>数据库业务流测试</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>business_flow</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>testcase/business_flow_test.py</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>数据库</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>sysbench</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BF-003</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>存储业务流测试</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>business_flow</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>必选</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>testcase/business_flow_test.py</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>NFS Server</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fio</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BF-004</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>视频流业务流测试</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>business_flow</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>testcase/business_flow_test.py</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>视频流</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>nginx-rtmp</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ffmpeg</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BF-005</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>消息队列业务流测试</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>business_flow</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>testcase/business_flow_test.py</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>消息队列</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>producer/consumer</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BF-006</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>微服务RPC业务流测试</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>business_flow</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>kernel</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>testcase/business_flow_test.py</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>验证网卡稳定性</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>微服务</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>gRPC Server</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ghz</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
